--- a/testData/AutomationExcelPage.xlsx
+++ b/testData/AutomationExcelPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinut\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinut\eclipse-newworkspace\Opencartv121\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800A74BE-5BCD-4B52-B61B-7D75515898C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4A68B8-3C4B-4FE2-8A6D-D1E421A6D634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EA3F65F6-DCB3-45B3-B30A-AB19701DDB35}"/>
+    <workbookView xWindow="3768" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{EA3F65F6-DCB3-45B3-B30A-AB19701DDB35}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Email</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>kumar1234@gmail.com</t>
-  </si>
-  <si>
-    <t>arun789@gmail.com</t>
   </si>
   <si>
     <t>vinu789@gmail.com</t>
@@ -132,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -143,7 +140,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67642B9D-04D6-436F-B830-1F7A1169E0A1}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -483,54 +479,43 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
